--- a/data/output/evaluasi_14.xlsx
+++ b/data/output/evaluasi_14.xlsx
@@ -8,6 +8,17 @@
   </bookViews>
   <sheets>
     <sheet name="1400" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="1471" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="1401" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="1402" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="1404" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="1405" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="1410" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="1473" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="1403" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="1408" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="1406" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="1407" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,6 +436,1010 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>provinsi</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>14</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Riau</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>5.413575510410141</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>adhb_net_ekspor_q1-25</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Diskrepansi ADHB antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>14</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Riau</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>6.109896777233714</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>adhb_net_ekspor_q2-25</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Diskrepansi ADHB antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>14</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Riau</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>6.12194447402251</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>adhb_net_ekspor_q3-25</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Diskrepansi ADHB antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>14</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Riau</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-10.19642351071043</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q2-25 vs q-to-q_pklnprt_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>14</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Riau</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-21.31839815632492</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q1-25 vs q-to-q_pkp_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>14</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Riau</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>1.922847753121258</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25 vs q-to-q_pkp_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>14</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Riau</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-6.321755698108385</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q2-25 vs y-on-y_pkp_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>14</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Riau</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-1.815678277286177</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q2-25 vs c-to-c_pkp_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>14</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Riau</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>-0.2723301777416389</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25 vs c-to-c_pkp_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1408</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Bengkalis</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>20.01492290222741</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1408</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Bengkalis</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>2.59443524121393</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1408</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Bengkalis</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.8850503630145442</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q3-25_prov vs implisit_q-to-q_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1408</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Bengkalis</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-5.293836939453532</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_q3-25_prov vs implisit_y-on-y_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1406</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Kampar</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0.5736578318615497</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1407</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Rokan Hulu</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0.6237261405063323</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1407</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Rokan Hulu</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>7.759944595659355</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_q3-25_prov vs implisit_y-on-y_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1471</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kota Pekanbaru</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-3.469268800863605</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q1-25_ril vs sog_q_pi_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1471</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kota Pekanbaru</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>4.190292804851028</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q2-25_ril vs sog_q_pi_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1471</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kota Pekanbaru</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-2.334722022707498</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q3-25_prov vs q-to-q_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1471</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kota Pekanbaru</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0.7248388871448883</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q3-25_prov vs q-to-q_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1471</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kota Pekanbaru</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0.1638402555414917</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1471</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kota Pekanbaru</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-4.584899201275705</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q3-25</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1401</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Kuantan Singingi</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>1.312118669045489</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q3-25_prov vs q-to-q_pkrt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1401</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Kuantan Singingi</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-7.692350348765014</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q3-25_prov vs q-to-q_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1401</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Kuantan Singingi</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-1.511382109478896</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q3-25_prov vs q-to-q_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1401</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Kuantan Singingi</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-1.053215423653796</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -436,7 +1451,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>provinsi</t>
+          <t>kabupaten/kota</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -462,85 +1477,651 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>14</v>
+        <v>1402</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Riau</t>
+          <t>Kabupaten Indragiri Hulu</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>6.218417586201536</v>
+        <v>-9.416921469870438</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>adhb_net_ekspor_q1-25</t>
+          <t>q-to-q_pklnprt_q3-25_prov vs q-to-q_pklnprt_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Diskrepansi lebih dari +- 5 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>14</v>
+        <v>1402</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Riau</t>
+          <t>Kabupaten Indragiri Hulu</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q2-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>6.727186246802577</v>
+        <v>-3.7511732610914</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>adhb_net_ekspor_q2-25</t>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Diskrepansi lebih dari +- 5 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>14</v>
+        <v>1402</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Riau</t>
+          <t>Kabupaten Indragiri Hulu</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>q2-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1.050036327069109</v>
+        <v>-0.1299823570000045</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>implisit_y-on-y_pkp_q2-25 vs implisit_y-on-y_pkp_q2-25.1</t>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Growth lebih dari +- 2 kalinya</t>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1404</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Pelalawan</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-1.882393117390513</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1404</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Pelalawan</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-2.109999999999994</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1405</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Siak</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>4.909480967358017</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1405</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Siak</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.04430588613288265</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q3-25_prov vs c-to-c_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1410</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Kepulauan Meranti</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>10.26051355918598</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1410</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Kepulauan Meranti</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0.6306598031233331</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1473</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kota Dumai</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.03158110067967665</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q3-25_prov vs q-to-q_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1473</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kota Dumai</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.8917278656953362</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q3-25_prov vs y-on-y_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1473</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kota Dumai</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-1.358769499548897</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1473</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kota Dumai</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.3073069073535625</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q3-25_prov vs c-to-c_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1473</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kota Dumai</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.05681847386710402</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q3-25_prov vs implisit_q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1403</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Indragiri Hilir</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-2.369643403900001</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>

--- a/data/output/evaluasi_14.xlsx
+++ b/data/output/evaluasi_14.xlsx
@@ -579,7 +579,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -607,7 +607,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -635,7 +635,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -663,7 +663,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -691,7 +691,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -719,7 +719,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
